--- a/Result/profitability/2351.xlsx
+++ b/Result/profitability/2351.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.34</v>
       </c>
       <c r="M2" t="n">
-        <v>0.60375</v>
+        <v>0.695</v>
       </c>
       <c r="N2" t="n">
-        <v>14.51875</v>
+        <v>15.1475</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>0.56875</v>
+        <v>0.675</v>
       </c>
       <c r="N3" t="n">
-        <v>14.465</v>
+        <v>15.475</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.66</v>
       </c>
       <c r="M4" t="n">
-        <v>0.55875</v>
+        <v>0.68</v>
       </c>
       <c r="N4" t="n">
-        <v>14.27875</v>
+        <v>15.04625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.95</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3625</v>
+        <v>0.59</v>
       </c>
       <c r="N5" t="n">
-        <v>11.2225</v>
+        <v>12.50125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.395</v>
+        <v>0.5337500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>11.16375</v>
+        <v>12.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3625</v>
+        <v>0.46125</v>
       </c>
       <c r="N7" t="n">
-        <v>11.3675</v>
+        <v>11.9825</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.76</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3575</v>
+        <v>0.40375</v>
       </c>
       <c r="N8" t="n">
-        <v>11.66875</v>
+        <v>11.86875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2351</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3559</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2822</v>
+      </c>
+      <c r="E75" t="n">
+        <v>737</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="G75" t="n">
+        <v>417</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.71%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>414</v>
+      </c>
+      <c r="K75" t="n">
+        <v>303</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.18375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3700000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3032786885245902</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.599999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08368200836820061</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-7.913043478260869</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.9752144899904669</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
